--- a/artifacts/关键标准答案.xlsx
+++ b/artifacts/关键标准答案.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="R7df233a3b3b9471d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="R7dafac7c308f4c2a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="R6511b250f29b4a3a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="R9df9e34b0a004b93"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="R7a9dac982f9d4f4b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="R84255bbe9d60449d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="R642b0c9c1a9f4f7b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="Rd64ad6adb917464f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="R129eb21d93d34aa2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="Rcf064d1d4aa2462e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -889,7 +889,7 @@
     </x:row>
     <x:row r="8" ht="78" customHeight="1">
       <x:c r="A8" s="35" t="str">
-        <x:v>reference_members</x:v>
+        <x:v>delivery_paths</x:v>
       </x:c>
       <x:c r="B8" s="36" t="str">
         <x:v>src/compile_push_templates.mjs,reports/template_locale_matrix.csv,reports/placeholder_mismatches.csv,reports/fallback_decisions.csv,reports/render_samples.csv</x:v>
@@ -898,7 +898,7 @@
         <x:v>相对路径逐字匹配</x:v>
       </x:c>
       <x:c r="D8" s="37" t="str">
-        <x:v>reference.zip成员</x:v>
+        <x:v>Prompt声明的业务交付路径</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
